--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AU5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46177.54166666666</v>
+        <v>46177.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -837,12 +837,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46177.625</v>
+        <v>46177.54166666666</v>
       </c>
     </row>
     <row r="4">
@@ -996,156 +996,315 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hassania Agadir</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FUS Rabat</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>46177.625</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Morocco Botola Pro</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>FAR Rabat</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Difaâ El Jadida</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="3" t="n">
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="3" t="n">
         <v>46177.70833333334</v>
       </c>
     </row>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
         <v>3.64</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -731,7 +731,7 @@
         <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q2" t="n">
         <v>3.64</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="Q2" t="n">
         <v>3.64</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="P2" t="n">
         <v>2.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.64</v>
+        <v>3.23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="S2" t="n">
         <v>1.74</v>
@@ -749,34 +749,34 @@
         <v>4.23</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Z2" t="n">
         <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF2" t="n">
         <v>2.64</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -728,7 +728,7 @@
         <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="P2" t="n">
         <v>2.78</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1046,10 +1046,10 @@
         <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="P4" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -731,7 +731,7 @@
         <v>2.58</v>
       </c>
       <c r="P2" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="Q2" t="n">
         <v>3.23</v>
@@ -1046,10 +1046,10 @@
         <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>10.76</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.37</v>
+        <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1046,10 +1046,10 @@
         <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="P4" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>10.76</v>
+        <v>10.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -731,7 +731,7 @@
         <v>2.58</v>
       </c>
       <c r="P2" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
         <v>3.23</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -731,7 +731,7 @@
         <v>2.58</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="Q2" t="n">
         <v>3.23</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46177.41666666666</v>
+        <v>46177.375</v>
       </c>
     </row>
     <row r="3">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>4.48</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>2.87</v>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -731,7 +731,7 @@
         <v>2.58</v>
       </c>
       <c r="P2" t="n">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="Q2" t="n">
         <v>3.23</v>
@@ -1043,49 +1043,49 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>2.87</v>
+        <v>2.54</v>
       </c>
       <c r="P4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1205,10 +1205,10 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P5" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -1046,10 +1046,10 @@
         <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="P4" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -861,36 +861,36 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>4.48</v>
+        <v>3.7</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52', '83']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '89']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46177.54166666666</v>

--- a/jogos_2026-06-04.xlsx
+++ b/jogos_2026-06-04.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46177.375</v>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46177.625</v>
@@ -1179,36 +1179,36 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="O5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="P5" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,68 +1241,68 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>['33', '71']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" t="n">
         <v>2</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-1</v>
-      </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46177.70833333334</v>
